--- a/artfynd/A 37951-2025 artfynd.xlsx
+++ b/artfynd/A 37951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147294</v>
       </c>
       <c r="B2" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129147177</v>
       </c>
       <c r="B4" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129146955</v>
       </c>
       <c r="B5" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>129147427</v>
       </c>
       <c r="B6" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129147250</v>
+        <v>129147273</v>
       </c>
       <c r="B8" t="n">
-        <v>75029</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352288</v>
+        <v>352275</v>
       </c>
       <c r="R8" t="n">
-        <v>6614567</v>
+        <v>6614539</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1363,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147273</v>
+        <v>129147250</v>
       </c>
       <c r="B10" t="n">
-        <v>91497</v>
+        <v>75029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1509,21 +1504,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352275</v>
+        <v>352288</v>
       </c>
       <c r="R10" t="n">
-        <v>6614539</v>
+        <v>6614567</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1572,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,7 +1602,7 @@
         <v>129147357</v>
       </c>
       <c r="B11" t="n">
-        <v>97290</v>
+        <v>97297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37951-2025 artfynd.xlsx
+++ b/artfynd/A 37951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147294</v>
       </c>
       <c r="B2" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129147177</v>
       </c>
       <c r="B4" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129146955</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129147427</v>
+        <v>129146997</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>75159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352317</v>
+        <v>352346</v>
       </c>
       <c r="R6" t="n">
-        <v>6614575</v>
+        <v>6614601</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129146997</v>
+        <v>129147427</v>
       </c>
       <c r="B7" t="n">
-        <v>75157</v>
+        <v>91506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352346</v>
+        <v>352317</v>
       </c>
       <c r="R7" t="n">
-        <v>6614601</v>
+        <v>6614575</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129147273</v>
+        <v>129147250</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>75031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352275</v>
+        <v>352288</v>
       </c>
       <c r="R8" t="n">
-        <v>6614539</v>
+        <v>6614567</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1363,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129147396</v>
+        <v>129147273</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>91506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,28 +1406,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1430,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352301</v>
+        <v>352275</v>
       </c>
       <c r="R9" t="n">
-        <v>6614534</v>
+        <v>6614539</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1493,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147250</v>
+        <v>129147396</v>
       </c>
       <c r="B10" t="n">
-        <v>75029</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,26 +1507,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352288</v>
+        <v>352301</v>
       </c>
       <c r="R10" t="n">
-        <v>6614567</v>
+        <v>6614534</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1567,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,7 +1602,7 @@
         <v>129147357</v>
       </c>
       <c r="B11" t="n">
-        <v>97297</v>
+        <v>97299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37951-2025 artfynd.xlsx
+++ b/artfynd/A 37951-2025 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129146997</v>
+        <v>129147427</v>
       </c>
       <c r="B6" t="n">
-        <v>75159</v>
+        <v>91506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352346</v>
+        <v>352317</v>
       </c>
       <c r="R6" t="n">
-        <v>6614601</v>
+        <v>6614575</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129147427</v>
+        <v>129146997</v>
       </c>
       <c r="B7" t="n">
-        <v>91506</v>
+        <v>75159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352317</v>
+        <v>352346</v>
       </c>
       <c r="R7" t="n">
-        <v>6614575</v>
+        <v>6614601</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
